--- a/Listado-de-inscriptos-(25338-70949).xlsx
+++ b/Listado-de-inscriptos-(25338-70949).xlsx
@@ -64,12 +64,540 @@
     <t xml:space="preserve">Estado de Inscripción </t>
   </si>
   <si>
+    <t xml:space="preserve">GR-0028567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILARDONI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS FABIAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carlfab64@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0014669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIBERATORE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREA ESTHER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">andrea.liberatore2@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0009452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORGELINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jorpasso@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIYLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0002856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GALATRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIELA ALEJANDRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daniela.a.galatro@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0056894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILLALBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAVIER ALEJANDRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ja.vill4lba@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0113526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACEDRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCILA ANDREA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">macedralucila@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0131827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALONSO CABRAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUTH MARINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ruth.alonsoc@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0108800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA VICTORIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">victoriakac@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0123507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHILIGUAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIANA MABEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eliana.chiliguay@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0062793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DE GOITIZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SABRINA NOELIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sabry_2007_18@Hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0102714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERREYRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MELISA CLARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melcferreyra@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0119860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAUJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOLEDAD ROCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soledad.r.araujo@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0113788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COUFFIGNAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SABRINA NOEMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">couffignalsabrina@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0120325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESAMOSCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROXANA ELIZABETH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roxibeth1992@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0112377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REYNOSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NICOLE MARTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nicolemreynoso@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0132674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEREZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YESICA DANIELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yesicadperezc@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0108439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEDINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLORENCIA AYELEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">medina.florencia.a95@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0112207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OHIENART</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAROLINA NATALIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c.ohienart@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0111162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONTECINOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARA MICAELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dara.montecinos@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUMANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVANA FLORENCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlorenciaHumano@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0113848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAINZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAXIMILIANO ANDRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sainzedicionuba@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0118428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORIANA AILEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oriana.ux@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0127782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LORENZO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULA CRISTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paulacristal.lorenzo@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0123778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TORRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THALIA MELODY DENNIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thalia-libra@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0117595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILAGROS BELEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">milagroscristina98@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0125214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WIRZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELEONORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eleonora.wirz@outlook.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0118607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAQUERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KARINA CHANTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">karinachantalvaquero@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0116443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DE SALVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIX LEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fenixescarlata99@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0128067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGUEZ DO CAMPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docamposofia21@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0125376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUHAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAFNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dafiduhay@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0117779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUTCHISON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEILA IARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hutchisonleila@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0118302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALZETTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO, STEFANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stefanocalzetti@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0117102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONCALI AGUIRRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIULIETTA ANAEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">giulietta.anael@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0118067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selenae205@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0125318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREITAS PERINO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOL EBONY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solfreitasperino@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0119269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORENO HARRAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA SOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solmorenoharrand@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0129534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOCCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIA ANTONELLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">antonoccoprime@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0122911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORA BORDON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA LAURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mmarymora1@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0126105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPINOZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LARA VICTORIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">laravictoriaespinoza@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0124971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAN MARTIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS ALEXANDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alex1sanmartinn@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0128912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAROLI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICTORIA CAMILA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">victoriabaroli@yahoo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0125414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIAGETTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIETA AYELEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">julibiagetti16@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0131943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERRER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIEN NAHIARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ferreraien2@gmail.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">GR-0122145</t>
   </si>
   <si>
-    <t xml:space="preserve">DNI</t>
-  </si>
-  <si>
     <t xml:space="preserve">ACOSTA</t>
   </si>
   <si>
@@ -79,39 +607,6 @@
     <t xml:space="preserve">acosta22brenda@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">ED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0124971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAN MARTIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARCOS ALEXANDER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alex1sanmartinn@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0014669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIBERATORE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANDREA ESTHER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">andrea.liberatore2@gmail.com</t>
-  </si>
-  <si>
     <t xml:space="preserve">GR-0131404</t>
   </si>
   <si>
@@ -124,6 +619,42 @@
     <t xml:space="preserve">andrionivale@gmail.com</t>
   </si>
   <si>
+    <t xml:space="preserve">GR-0125525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALENTINA DOMINIQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valentinapolack@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0125751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUINTANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFIA MAGALI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rezespl@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0126088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRAZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMILSE MAGALI MONSERRAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barrazaemilsemonserrat@gmail.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">GR-0127367</t>
   </si>
   <si>
@@ -136,271 +667,28 @@
     <t xml:space="preserve">annsantuchoauthor@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">GR-0129534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOCCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIA ANTONELLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">antonoccoprime@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0126088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARRAZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMILSE MAGALI MONSERRAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">barrazaemilsemonserrat@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0112207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OHIENART</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAROLINA NATALIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c.ohienart@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0028567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GILARDONI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARLOS FABIAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carlfab64@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0113788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COUFFIGNAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SABRINA NOEMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">couffignalsabrina@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0125376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUHAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAFNE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dafiduhay@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0002856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GALATRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DANIELA ALEJANDRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">daniela.a.galatro@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0111162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MONTECINOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DARA MICAELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dara.montecinos@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0128067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RODRIGUEZ DO CAMPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">docamposofia21@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0125214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WIRZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELEONORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eleonora.wirz@outlook.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0123507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHILIGUAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELIANA MABEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eliana.chiliguay@yahoo.com.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0116443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DE SALVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FELIX LEO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fenixescarlata99@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0131943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERRER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIEN NAHIARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ferreraien2@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUMANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVANA FLORENCIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FlorenciaHumano@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0117102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RONCALI AGUIRRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIULIETTA ANAEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">giulietta.anael@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0117779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUTCHISON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEILA IARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hutchisonleila@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0056894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VILLALBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JAVIER ALEJANDRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ja.vill4lba@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0009452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PASSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JORGELINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jorpasso@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIYLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0125414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIAGETTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JULIETA AYELEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">julibiagetti16@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0118607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAQUERO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KARINA CHANTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">karinachantalvaquero@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0126105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPINOZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LARA VICTORIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">laravictoriaespinoza@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0113526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MACEDRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUCILA ANDREA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">macedralucila@gmail.com</t>
+    <t xml:space="preserve">GR-0128257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUIZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAREN MILAGROS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mily0972@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR-0106785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEDINA ANTICONA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARLON JUNIOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phscmed24@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">GR-0125479</t>
@@ -415,16 +703,16 @@
     <t xml:space="preserve">majotorrico13@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">GR-0108439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEDINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLORENCIA AYELEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">medina.florencia.a95@gmail.com</t>
+    <t xml:space="preserve">GR-0126223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILORIA JIMENEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALERIA VALENTINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vvviloria2010@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">Medina</t>
@@ -434,294 +722,6 @@
   </si>
   <si>
     <t xml:space="preserve">medinaflorencia2022@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0102714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERREYRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MELISA CLARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melcferreyra@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0117595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRISTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MILAGROS BELEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">milagroscristina98@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0128257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUIZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAREN MILAGROS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mily0972@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0122911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MORA BORDON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIA LAURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mmarymora1@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0112377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REYNOSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NICOLE MARTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nicolemreynoso@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0118428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIAZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORIANA AILEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oriana.ux@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0127782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LORENZO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAULA CRISTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">paulacristal.lorenzo@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0106785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEDINA ANTICONA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARLON JUNIOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phscmed24@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0125751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUINTANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFIA MAGALI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rezespl@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0120325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PESAMOSCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROXANA ELIZABETH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roxibeth1992@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0131827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALONSO CABRAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUTH MARINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ruth.alonsoc@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0062793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DE GOITIZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SABRINA NOELIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sabry_2007_18@Hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0113848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAINZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAXIMILIANO ANDRES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sainzedicionuba@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0118067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELENA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selenae205@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0119860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARAUJO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOLEDAD ROCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soledad.r.araujo@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0125318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FREITAS PERINO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOL EBONY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">solfreitasperino@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0119269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MORENO HARRAND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIA SOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">solmorenoharrand@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0118302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALZETTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RODRIGO, STEFANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stefanocalzetti@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0123778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORRES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THALIA MELODY DENNIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thalia-libra@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0125525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLACK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALENTINA DOMINIQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valentinapolack@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0128912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAROLI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VICTORIA CAMILA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">victoriabaroli@yahoo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0108800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIA VICTORIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">victoriakac@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0126223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VILORIA JIMENEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALERIA VALENTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vvviloria2010@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-0132674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEREZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YESICA DANIELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yesicadperezc@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -825,27 +825,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1157,7 +1157,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>44263510</v>
+        <v>16823550</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>16</v>
@@ -1165,7 +1165,7 @@
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="5" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1186,7 +1186,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>43472939</v>
+        <v>22326925</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>23</v>
@@ -1194,7 +1194,7 @@
       <c r="E7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1215,7 +1215,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>22326925</v>
+        <v>26618542</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>27</v>
@@ -1223,11 +1223,11 @@
       <c r="E8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>20</v>
@@ -1238,22 +1238,22 @@
     </row>
     <row r="9" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>44342516</v>
+        <v>28630613</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>19</v>
@@ -1267,22 +1267,22 @@
     </row>
     <row r="10" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>46123398</v>
+        <v>30067218</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>19</v>
@@ -1296,22 +1296,22 @@
     </row>
     <row r="11" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>42988073</v>
+        <v>31239699</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>19</v>
@@ -1325,22 +1325,22 @@
     </row>
     <row r="12" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>45678876</v>
+        <v>31348736</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>19</v>
@@ -1354,22 +1354,22 @@
     </row>
     <row r="13" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>39775018</v>
+        <v>33669792</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>19</v>
@@ -1383,22 +1383,22 @@
     </row>
     <row r="14" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>16823550</v>
+        <v>33778389</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="5" t="s">
         <v>53</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>19</v>
@@ -1412,22 +1412,22 @@
     </row>
     <row r="15" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>36747356</v>
+        <v>34235820</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>19</v>
@@ -1441,22 +1441,22 @@
     </row>
     <row r="16" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>42251722</v>
+        <v>35428364</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>19</v>
@@ -1470,22 +1470,22 @@
     </row>
     <row r="17" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>28630613</v>
+        <v>35837001</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>19</v>
@@ -1499,22 +1499,22 @@
     </row>
     <row r="18" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>39812352</v>
+        <v>36747356</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>19</v>
@@ -1528,22 +1528,22 @@
     </row>
     <row r="19" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>42147937</v>
+        <v>37234647</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>19</v>
@@ -1557,22 +1557,22 @@
     </row>
     <row r="20" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>41041450</v>
+        <v>38150397</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>19</v>
@@ -1586,22 +1586,22 @@
     </row>
     <row r="21" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>33778389</v>
+        <v>38346733</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>19</v>
@@ -1615,22 +1615,22 @@
     </row>
     <row r="22" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>41800096</v>
+        <v>38994172</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>19</v>
@@ -1644,22 +1644,22 @@
     </row>
     <row r="23" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>44098220</v>
+        <v>39775018</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>19</v>
@@ -1673,22 +1673,22 @@
     </row>
     <row r="24" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>40394823</v>
+        <v>39812352</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>19</v>
@@ -1702,22 +1702,22 @@
     </row>
     <row r="25" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>42591463</v>
+        <v>40394823</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>19</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="26" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>42417376</v>
+        <v>40540541</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>19</v>
@@ -1760,22 +1760,22 @@
     </row>
     <row r="27" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>30067218</v>
+        <v>40623095</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>19</v>
@@ -1789,25 +1789,25 @@
     </row>
     <row r="28" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>26618542</v>
+        <v>40631907</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>20</v>
@@ -1824,7 +1824,7 @@
         <v>15</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>43866889</v>
+        <v>40720748</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>112</v>
@@ -1853,7 +1853,7 @@
         <v>15</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>41713894</v>
+        <v>40729559</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>116</v>
@@ -1882,7 +1882,7 @@
         <v>15</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>43385055</v>
+        <v>41041450</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>120</v>
@@ -1911,7 +1911,7 @@
         <v>15</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>31239699</v>
+        <v>41713894</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>124</v>
@@ -1940,7 +1940,7 @@
         <v>15</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>94217396</v>
+        <v>41800096</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>128</v>
@@ -1969,7 +1969,7 @@
         <v>15</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>38994172</v>
+        <v>42147937</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>132</v>
@@ -1991,34 +1991,52 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>42251722</v>
+      </c>
       <c r="D35" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F35" s="6" t="s">
         <v>137</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>35428364</v>
+        <v>42417376</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>19</v>
@@ -2032,22 +2050,22 @@
     </row>
     <row r="37" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>40729559</v>
+        <v>42571104</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>19</v>
@@ -2061,22 +2079,22 @@
     </row>
     <row r="38" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>46194990</v>
+        <v>42591463</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>19</v>
@@ -2090,22 +2108,22 @@
     </row>
     <row r="39" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>43093093</v>
+        <v>42660539</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>19</v>
@@ -2119,22 +2137,22 @@
     </row>
     <row r="40" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>38150397</v>
+        <v>42720845</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>19</v>
@@ -2148,22 +2166,22 @@
     </row>
     <row r="41" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>40623095</v>
+        <v>42969719</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>19</v>
@@ -2177,22 +2195,22 @@
     </row>
     <row r="42" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>40631907</v>
+        <v>42988073</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>19</v>
@@ -2206,22 +2224,22 @@
     </row>
     <row r="43" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>94057669</v>
+        <v>43093093</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>19</v>
@@ -2235,22 +2253,22 @@
     </row>
     <row r="44" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>44507778</v>
+        <v>43385055</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>19</v>
@@ -2264,22 +2282,22 @@
     </row>
     <row r="45" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>37234647</v>
+        <v>43472939</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>19</v>
@@ -2293,22 +2311,22 @@
     </row>
     <row r="46" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>31348736</v>
+        <v>43573154</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>19</v>
@@ -2322,22 +2340,22 @@
     </row>
     <row r="47" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>34235820</v>
+        <v>43866889</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>19</v>
@@ -2351,22 +2369,22 @@
     </row>
     <row r="48" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>40540541</v>
+        <v>44098220</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>19</v>
@@ -2380,22 +2398,22 @@
     </row>
     <row r="49" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>42660539</v>
+        <v>44263510</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>19</v>
@@ -2409,22 +2427,22 @@
     </row>
     <row r="50" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>35837001</v>
+        <v>44342516</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>19</v>
@@ -2438,22 +2456,22 @@
     </row>
     <row r="51" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>42720845</v>
+        <v>44364712</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>19</v>
@@ -2467,22 +2485,22 @@
     </row>
     <row r="52" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>42969719</v>
+        <v>44507778</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>19</v>
@@ -2496,22 +2514,22 @@
     </row>
     <row r="53" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>42571104</v>
+        <v>45678876</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>19</v>
@@ -2525,22 +2543,22 @@
     </row>
     <row r="54" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>40720748</v>
+        <v>46123398</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>19</v>
@@ -2554,22 +2572,22 @@
     </row>
     <row r="55" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>44364712</v>
+        <v>46194990</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>19</v>
@@ -2583,22 +2601,22 @@
     </row>
     <row r="56" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>43573154</v>
+        <v>94057669</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>19</v>
@@ -2612,22 +2630,22 @@
     </row>
     <row r="57" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>33669792</v>
+        <v>94217396</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>19</v>
@@ -2641,7 +2659,7 @@
     </row>
     <row r="58" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>15</v>
@@ -2650,13 +2668,13 @@
         <v>96024277</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>19</v>
@@ -2669,32 +2687,14 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="22.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>38346733</v>
-      </c>
       <c r="D59" s="1" t="s">
         <v>231</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -2706,12 +2706,11 @@
     <mergeCell ref="E3:H3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F8" r:id="rId1" display="andrea.liberatore2@gmail.com"/>
-    <hyperlink ref="F14" display="carlfab64@gmail.com"/>
+    <hyperlink ref="F7" r:id="rId1" display="andrea.liberatore2@gmail.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="atEnd" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
